--- a/wildlife/reports/United-Kingdom/trend/Oxford/Birds/Street-Pigeon.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Oxford/Birds/Street-Pigeon.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/wildlife/reports/United-Kingdom/trend/Oxford/Birds/Street-Pigeon.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Oxford/Birds/Street-Pigeon.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/wildlife/reports/United-Kingdom/trend/Oxford/Birds/Street-Pigeon.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Oxford/Birds/Street-Pigeon.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/wildlife/reports/United-Kingdom/trend/Oxford/Birds/Street-Pigeon.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Oxford/Birds/Street-Pigeon.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
